--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J326"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12178,6 +12178,78 @@
         <v>393.55</v>
       </c>
       <c r="J326" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="C327" t="n">
+        <v>389.79</v>
+      </c>
+      <c r="D327" t="n">
+        <v>390.65</v>
+      </c>
+      <c r="E327" t="n">
+        <v>396.37</v>
+      </c>
+      <c r="F327" t="n">
+        <v>400.23</v>
+      </c>
+      <c r="G327" t="n">
+        <v>402.5</v>
+      </c>
+      <c r="H327" t="n">
+        <v>399.73</v>
+      </c>
+      <c r="I327" t="n">
+        <v>392.39</v>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>372.97</v>
+      </c>
+      <c r="C328" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="D328" t="n">
+        <v>388.4</v>
+      </c>
+      <c r="E328" t="n">
+        <v>395.39</v>
+      </c>
+      <c r="F328" t="n">
+        <v>398.74</v>
+      </c>
+      <c r="G328" t="n">
+        <v>401.43</v>
+      </c>
+      <c r="H328" t="n">
+        <v>398.68</v>
+      </c>
+      <c r="I328" t="n">
+        <v>391.11</v>
+      </c>
+      <c r="J328" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12194,7 +12266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B335"/>
+  <dimension ref="A1:B337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15547,6 +15619,26 @@
       </c>
       <c r="B335" t="n">
         <v>0.83</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>-0.75</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>0.59</v>
       </c>
     </row>
   </sheetData>
@@ -15715,28 +15807,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.04366799800032466</v>
+        <v>0.03686536763297864</v>
       </c>
       <c r="J2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K2" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L2" t="n">
-        <v>0.006297951139159097</v>
+        <v>0.004515462340353604</v>
       </c>
       <c r="M2" t="n">
-        <v>3.12426425275424</v>
+        <v>3.135013052510141</v>
       </c>
       <c r="N2" t="n">
-        <v>16.2793323541907</v>
+        <v>16.35055783930829</v>
       </c>
       <c r="O2" t="n">
-        <v>4.034765464582879</v>
+        <v>4.04358230277415</v>
       </c>
       <c r="P2" t="n">
-        <v>377.1430214242816</v>
+        <v>377.2150372294447</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15797,28 +15889,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06981017878291991</v>
+        <v>0.06356951536344413</v>
       </c>
       <c r="J3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K3" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01731974486432697</v>
+        <v>0.01446873606267463</v>
       </c>
       <c r="M3" t="n">
-        <v>3.079891666396759</v>
+        <v>3.095301079885318</v>
       </c>
       <c r="N3" t="n">
-        <v>14.96102567002999</v>
+        <v>15.02106599796092</v>
       </c>
       <c r="O3" t="n">
-        <v>3.867948509226821</v>
+        <v>3.875702000665289</v>
       </c>
       <c r="P3" t="n">
-        <v>391.6861650627098</v>
+        <v>391.7522383063242</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15879,28 +15971,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09768642068726117</v>
+        <v>0.09153814840323171</v>
       </c>
       <c r="J4" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K4" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03726276863326072</v>
+        <v>0.03298500591094267</v>
       </c>
       <c r="M4" t="n">
-        <v>2.985796108127109</v>
+        <v>2.992970618463622</v>
       </c>
       <c r="N4" t="n">
-        <v>13.3399490007235</v>
+        <v>13.4055312831553</v>
       </c>
       <c r="O4" t="n">
-        <v>3.65238949192491</v>
+        <v>3.661356481299697</v>
       </c>
       <c r="P4" t="n">
-        <v>391.7375773855173</v>
+        <v>391.8026724697239</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -15961,28 +16053,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03609324207700023</v>
+        <v>0.03164913547535218</v>
       </c>
       <c r="J5" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K5" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00610659487335008</v>
+        <v>0.00474045140591639</v>
       </c>
       <c r="M5" t="n">
-        <v>2.684245465844433</v>
+        <v>2.689554016403188</v>
       </c>
       <c r="N5" t="n">
-        <v>11.47217112860363</v>
+        <v>11.47634243432151</v>
       </c>
       <c r="O5" t="n">
-        <v>3.387059363017369</v>
+        <v>3.387675078032354</v>
       </c>
       <c r="P5" t="n">
-        <v>398.4061683469965</v>
+        <v>398.4532186055022</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16043,28 +16135,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1000207574177241</v>
+        <v>0.09906331579916934</v>
       </c>
       <c r="J6" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K6" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03401153389102041</v>
+        <v>0.03384759031346563</v>
       </c>
       <c r="M6" t="n">
-        <v>2.860461562491124</v>
+        <v>2.847955807823687</v>
       </c>
       <c r="N6" t="n">
-        <v>15.37372570182128</v>
+        <v>15.28645380215013</v>
       </c>
       <c r="O6" t="n">
-        <v>3.920934289403647</v>
+        <v>3.909789483098819</v>
       </c>
       <c r="P6" t="n">
-        <v>397.5596568785789</v>
+        <v>397.5697971805938</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16125,28 +16217,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.03336506779362781</v>
+        <v>0.02847286376962425</v>
       </c>
       <c r="J7" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K7" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005093406696889735</v>
+        <v>0.00374041306591788</v>
       </c>
       <c r="M7" t="n">
-        <v>2.633720222176228</v>
+        <v>2.640553261011261</v>
       </c>
       <c r="N7" t="n">
-        <v>11.76551942283234</v>
+        <v>11.7836108148843</v>
       </c>
       <c r="O7" t="n">
-        <v>3.430090293685042</v>
+        <v>3.432726440438314</v>
       </c>
       <c r="P7" t="n">
-        <v>404.9135838958882</v>
+        <v>404.9653781831645</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16207,28 +16299,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.05752748964197369</v>
+        <v>0.04516433220215896</v>
       </c>
       <c r="J8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K8" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L8" t="n">
-        <v>0.01671941149755041</v>
+        <v>0.00998928253943554</v>
       </c>
       <c r="M8" t="n">
-        <v>2.474424476757823</v>
+        <v>2.528511142784442</v>
       </c>
       <c r="N8" t="n">
-        <v>10.53077788020263</v>
+        <v>11.03214413188876</v>
       </c>
       <c r="O8" t="n">
-        <v>3.24511600412106</v>
+        <v>3.321467165559335</v>
       </c>
       <c r="P8" t="n">
-        <v>407.3704927533396</v>
+        <v>407.5013779909883</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16289,28 +16381,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.02555158343216537</v>
+        <v>-0.03660295233076522</v>
       </c>
       <c r="J9" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="K9" t="n">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003651999532261141</v>
+        <v>0.007235354440544572</v>
       </c>
       <c r="M9" t="n">
-        <v>2.49929094831499</v>
+        <v>2.540956843167064</v>
       </c>
       <c r="N9" t="n">
-        <v>9.637604615299439</v>
+        <v>10.03186931399001</v>
       </c>
       <c r="O9" t="n">
-        <v>3.104449164553905</v>
+        <v>3.167312632815083</v>
       </c>
       <c r="P9" t="n">
-        <v>401.1037367013911</v>
+        <v>401.2207353977142</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16352,7 +16444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J326"/>
+  <dimension ref="A1:J328"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33307,6 +33399,110 @@
         </is>
       </c>
     </row>
+    <row r="327">
+      <c r="A327" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-25 22:10:44+00:00</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>-35.434345729448225,174.36201821579448</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>-35.43498428682724,174.36229747250258</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>-35.4355737947081,174.36271808313677</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>-35.43614076282484,174.36321181814134</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>-35.436611897590595,174.363818778933</t>
+        </is>
+      </c>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>-35.43703914894156,174.3644582459868</t>
+        </is>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>-35.437367370980596,174.36512855098132</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>-35.43754908808545,174.36593336799058</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:55+00:00</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>-35.434345729448225,174.36201821579448</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>-35.43499089778574,174.36227380857514</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>-35.43558414937976,174.36269677129476</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>-35.43614617626003,174.3632032869499</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>-35.43662167042632,174.3638075187311</t>
+        </is>
+      </c>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>-35.437047121189316,174.36445161035508</t>
+        </is>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>-35.437376328038646,174.3651248100432</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>-35.43756046186776,174.3659309883806</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12250,6 +12250,78 @@
         <v>391.11</v>
       </c>
       <c r="J328" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="C329" t="n">
+        <v>386.29</v>
+      </c>
+      <c r="D329" t="n">
+        <v>388.03</v>
+      </c>
+      <c r="E329" t="n">
+        <v>395.34</v>
+      </c>
+      <c r="F329" t="n">
+        <v>398.78</v>
+      </c>
+      <c r="G329" t="n">
+        <v>401.99</v>
+      </c>
+      <c r="H329" t="n">
+        <v>398.88</v>
+      </c>
+      <c r="I329" t="n">
+        <v>389.68</v>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="C330" t="n">
+        <v>388.82</v>
+      </c>
+      <c r="D330" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="E330" t="n">
+        <v>397.23</v>
+      </c>
+      <c r="F330" t="n">
+        <v>400.62</v>
+      </c>
+      <c r="G330" t="n">
+        <v>403.6</v>
+      </c>
+      <c r="H330" t="n">
+        <v>400.87</v>
+      </c>
+      <c r="I330" t="n">
+        <v>391.26</v>
+      </c>
+      <c r="J330" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12266,7 +12338,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B337"/>
+  <dimension ref="A1:B339"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15639,6 +15711,26 @@
       </c>
       <c r="B337" t="n">
         <v>0.59</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>0.47</v>
       </c>
     </row>
   </sheetData>
@@ -15807,28 +15899,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03686536763297864</v>
+        <v>0.02952187275405713</v>
       </c>
       <c r="J2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004515462340353604</v>
+        <v>0.002905650437928675</v>
       </c>
       <c r="M2" t="n">
-        <v>3.135013052510141</v>
+        <v>3.147829597286465</v>
       </c>
       <c r="N2" t="n">
-        <v>16.35055783930829</v>
+        <v>16.45877092669832</v>
       </c>
       <c r="O2" t="n">
-        <v>4.04358230277415</v>
+        <v>4.056941080013157</v>
       </c>
       <c r="P2" t="n">
-        <v>377.2150372294447</v>
+        <v>377.2930434921844</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15889,28 +15981,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.06356951536344413</v>
+        <v>0.0561464102833093</v>
       </c>
       <c r="J3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K3" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01446873606267463</v>
+        <v>0.01132364409478059</v>
       </c>
       <c r="M3" t="n">
-        <v>3.095301079885318</v>
+        <v>3.116766461402797</v>
       </c>
       <c r="N3" t="n">
-        <v>15.02106599796092</v>
+        <v>15.1470699251617</v>
       </c>
       <c r="O3" t="n">
-        <v>3.875702000665289</v>
+        <v>3.891923679257046</v>
       </c>
       <c r="P3" t="n">
-        <v>391.7522383063242</v>
+        <v>391.8310879076215</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -15971,28 +16063,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.09153814840323171</v>
+        <v>0.08495563308570266</v>
       </c>
       <c r="J4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K4" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L4" t="n">
-        <v>0.03298500591094267</v>
+        <v>0.02859476545297557</v>
       </c>
       <c r="M4" t="n">
-        <v>2.992970618463622</v>
+        <v>3.002150087019714</v>
       </c>
       <c r="N4" t="n">
-        <v>13.4055312831553</v>
+        <v>13.49320023425325</v>
       </c>
       <c r="O4" t="n">
-        <v>3.661356481299697</v>
+        <v>3.673309166712387</v>
       </c>
       <c r="P4" t="n">
-        <v>391.8026724697239</v>
+        <v>391.872593951677</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16053,28 +16145,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03164913547535218</v>
+        <v>0.02785276470817605</v>
       </c>
       <c r="J5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K5" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00474045140591639</v>
+        <v>0.003709498108301901</v>
       </c>
       <c r="M5" t="n">
-        <v>2.689554016403188</v>
+        <v>2.691525428163746</v>
       </c>
       <c r="N5" t="n">
-        <v>11.47634243432151</v>
+        <v>11.46632269987038</v>
       </c>
       <c r="O5" t="n">
-        <v>3.387675078032354</v>
+        <v>3.386195903941527</v>
       </c>
       <c r="P5" t="n">
-        <v>398.4532186055022</v>
+        <v>398.4935426152732</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16135,28 +16227,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09906331579916934</v>
+        <v>0.0984006582211366</v>
       </c>
       <c r="J6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K6" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03384759031346563</v>
+        <v>0.03386846605522753</v>
       </c>
       <c r="M6" t="n">
-        <v>2.847955807823687</v>
+        <v>2.836567356564505</v>
       </c>
       <c r="N6" t="n">
-        <v>15.28645380215013</v>
+        <v>15.20034483230609</v>
       </c>
       <c r="O6" t="n">
-        <v>3.909789483098819</v>
+        <v>3.898761961482913</v>
       </c>
       <c r="P6" t="n">
-        <v>397.5697971805938</v>
+        <v>397.576831327081</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16217,28 +16309,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02847286376962425</v>
+        <v>0.02478507244591414</v>
       </c>
       <c r="J7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K7" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00374041306591788</v>
+        <v>0.002864701858690699</v>
       </c>
       <c r="M7" t="n">
-        <v>2.640553261011261</v>
+        <v>2.642026376368174</v>
       </c>
       <c r="N7" t="n">
-        <v>11.7836108148843</v>
+        <v>11.76716245041624</v>
       </c>
       <c r="O7" t="n">
-        <v>3.432726440438314</v>
+        <v>3.430329787413485</v>
       </c>
       <c r="P7" t="n">
-        <v>404.9653781831645</v>
+        <v>405.0045495541903</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16299,28 +16391,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.04516433220215896</v>
+        <v>0.03404855538920638</v>
       </c>
       <c r="J8" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K8" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00998928253943554</v>
+        <v>0.005547633668859797</v>
       </c>
       <c r="M8" t="n">
-        <v>2.528511142784442</v>
+        <v>2.577226380257671</v>
       </c>
       <c r="N8" t="n">
-        <v>11.03214413188876</v>
+        <v>11.4364252136571</v>
       </c>
       <c r="O8" t="n">
-        <v>3.321467165559335</v>
+        <v>3.381778409898718</v>
       </c>
       <c r="P8" t="n">
-        <v>407.5013779909883</v>
+        <v>407.6194571160108</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16381,28 +16473,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.03660295233076522</v>
+        <v>-0.04888590369754208</v>
       </c>
       <c r="J9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="K9" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="L9" t="n">
-        <v>0.007235354440544572</v>
+        <v>0.01232091038516447</v>
       </c>
       <c r="M9" t="n">
-        <v>2.540956843167064</v>
+        <v>2.588741152433846</v>
       </c>
       <c r="N9" t="n">
-        <v>10.03186931399001</v>
+        <v>10.54282650101569</v>
       </c>
       <c r="O9" t="n">
-        <v>3.167312632815083</v>
+        <v>3.246971897170606</v>
       </c>
       <c r="P9" t="n">
-        <v>401.2207353977142</v>
+        <v>401.3512148301007</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16444,7 +16536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J328"/>
+  <dimension ref="A1:J330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33503,6 +33595,110 @@
         </is>
       </c>
     </row>
+    <row r="329">
+      <c r="A329" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-27 22:11:24+00:00</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>-35.43434750528098,174.36200216954268</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>-35.434994479933145,174.36226098626918</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>-35.435585852147625,174.3626932666802</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>-35.436146452455695,174.36320285168497</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>-35.43662140806831,174.3638078210184</t>
+        </is>
+      </c>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>-35.437042948798016,174.3644550832092</t>
+        </is>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>-35.437374621932356,174.3651255226029</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>-35.43757316851514,174.36592832990934</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-04 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>-35.43434541535514,174.36202105390697</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>-35.434987111774824,174.36228736060457</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>-35.43557669401653,174.36271211582158</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>-35.43613601225878,174.36321930469617</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>-35.43660933959987,174.3638217262337</t>
+        </is>
+      </c>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>-35.437030953172474,174.36446506766293</t>
+        </is>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>-35.437357646174604,174.36513261257036</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>-35.43755912900265,174.3659312672412</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0073/nzd0073.xlsx
+++ b/data/nzd0073/nzd0073.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J330"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12322,6 +12322,42 @@
         <v>391.26</v>
       </c>
       <c r="J330" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>373.72</v>
+      </c>
+      <c r="C331" t="n">
+        <v>388.67</v>
+      </c>
+      <c r="D331" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="E331" t="n">
+        <v>396.48</v>
+      </c>
+      <c r="F331" t="n">
+        <v>396.64</v>
+      </c>
+      <c r="G331" t="n">
+        <v>401.63</v>
+      </c>
+      <c r="H331" t="n">
+        <v>400.88</v>
+      </c>
+      <c r="I331" t="n">
+        <v>390.26</v>
+      </c>
+      <c r="J331" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12338,7 +12374,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B339"/>
+  <dimension ref="A1:B340"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15731,6 +15767,16 @@
       </c>
       <c r="B339" t="n">
         <v>0.47</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>-0.45</v>
       </c>
     </row>
   </sheetData>
@@ -15899,28 +15945,28 @@
         <v>0.08160000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>0.02952187275405713</v>
+        <v>0.02677639396757531</v>
       </c>
       <c r="J2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K2" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002905650437928675</v>
+        <v>0.002400524749214705</v>
       </c>
       <c r="M2" t="n">
-        <v>3.147829597286465</v>
+        <v>3.150133061602657</v>
       </c>
       <c r="N2" t="n">
-        <v>16.45877092669832</v>
+        <v>16.46626251441079</v>
       </c>
       <c r="O2" t="n">
-        <v>4.056941080013157</v>
+        <v>4.05786427993973</v>
       </c>
       <c r="P2" t="n">
-        <v>377.2930434921844</v>
+        <v>377.3223231230344</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -15981,28 +16027,28 @@
         <v>0.093</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0561464102833093</v>
+        <v>0.05321239837087963</v>
       </c>
       <c r="J3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K3" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01132364409478059</v>
+        <v>0.01021216738152786</v>
       </c>
       <c r="M3" t="n">
-        <v>3.116766461402797</v>
+        <v>3.123059022810321</v>
       </c>
       <c r="N3" t="n">
-        <v>15.1470699251617</v>
+        <v>15.16668566567764</v>
       </c>
       <c r="O3" t="n">
-        <v>3.891923679257046</v>
+        <v>3.894442921096372</v>
       </c>
       <c r="P3" t="n">
-        <v>391.8310879076215</v>
+        <v>391.8623781824284</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -16063,28 +16109,28 @@
         <v>0.1099</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08495563308570266</v>
+        <v>0.08181803114543756</v>
       </c>
       <c r="J4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K4" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02859476545297557</v>
+        <v>0.02662025062127993</v>
       </c>
       <c r="M4" t="n">
-        <v>3.002150087019714</v>
+        <v>3.006052258172955</v>
       </c>
       <c r="N4" t="n">
-        <v>13.49320023425325</v>
+        <v>13.52723541189853</v>
       </c>
       <c r="O4" t="n">
-        <v>3.673309166712387</v>
+        <v>3.677939016881401</v>
       </c>
       <c r="P4" t="n">
-        <v>391.872593951677</v>
+        <v>391.9060554473613</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -16145,28 +16191,28 @@
         <v>0.0961</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02785276470817605</v>
+        <v>0.02611696539940919</v>
       </c>
       <c r="J5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K5" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003709498108301901</v>
+        <v>0.003280069089142246</v>
       </c>
       <c r="M5" t="n">
-        <v>2.691525428163746</v>
+        <v>2.691652287616998</v>
       </c>
       <c r="N5" t="n">
-        <v>11.46632269987038</v>
+        <v>11.45450723265223</v>
       </c>
       <c r="O5" t="n">
-        <v>3.386195903941527</v>
+        <v>3.384450802220684</v>
       </c>
       <c r="P5" t="n">
-        <v>398.4935426152732</v>
+        <v>398.512054345628</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -16227,28 +16273,28 @@
         <v>0.0914</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0984006582211366</v>
+        <v>0.09614834792057174</v>
       </c>
       <c r="J6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K6" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03386846605522753</v>
+        <v>0.03253271724665829</v>
       </c>
       <c r="M6" t="n">
-        <v>2.836567356564505</v>
+        <v>2.83981709480619</v>
       </c>
       <c r="N6" t="n">
-        <v>15.20034483230609</v>
+        <v>15.19289139951221</v>
       </c>
       <c r="O6" t="n">
-        <v>3.898761961482913</v>
+        <v>3.89780597253278</v>
       </c>
       <c r="P6" t="n">
-        <v>397.576831327081</v>
+        <v>397.6008514777684</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -16309,28 +16355,28 @@
         <v>0.1852</v>
       </c>
       <c r="I7" t="n">
-        <v>0.02478507244591414</v>
+        <v>0.02224494100084288</v>
       </c>
       <c r="J7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K7" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002864701858690699</v>
+        <v>0.002315946814269276</v>
       </c>
       <c r="M7" t="n">
-        <v>2.642026376368174</v>
+        <v>2.646074301405644</v>
       </c>
       <c r="N7" t="n">
-        <v>11.76716245041624</v>
+        <v>11.78061051075083</v>
       </c>
       <c r="O7" t="n">
-        <v>3.430329787413485</v>
+        <v>3.432289397872917</v>
       </c>
       <c r="P7" t="n">
-        <v>405.0045495541903</v>
+        <v>405.0316392229899</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -16391,28 +16437,28 @@
         <v>0.1192</v>
       </c>
       <c r="I8" t="n">
-        <v>0.03404855538920638</v>
+        <v>0.02924313104657101</v>
       </c>
       <c r="J8" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K8" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005547633668859797</v>
+        <v>0.004065406747112976</v>
       </c>
       <c r="M8" t="n">
-        <v>2.577226380257671</v>
+        <v>2.598223766136634</v>
       </c>
       <c r="N8" t="n">
-        <v>11.4364252136571</v>
+        <v>11.57751592681134</v>
       </c>
       <c r="O8" t="n">
-        <v>3.381778409898718</v>
+        <v>3.402574896576319</v>
       </c>
       <c r="P8" t="n">
-        <v>407.6194571160108</v>
+        <v>407.670705390637</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -16473,28 +16519,28 @@
         <v>0.0886</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.04888590369754208</v>
+        <v>-0.05501977476461001</v>
       </c>
       <c r="J9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K9" t="n">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="L9" t="n">
-        <v>0.01232091038516447</v>
+        <v>0.0152576930228886</v>
       </c>
       <c r="M9" t="n">
-        <v>2.588741152433846</v>
+        <v>2.612967936901221</v>
       </c>
       <c r="N9" t="n">
-        <v>10.54282650101569</v>
+        <v>10.79722551661327</v>
       </c>
       <c r="O9" t="n">
-        <v>3.246971897170606</v>
+        <v>3.285913193712407</v>
       </c>
       <c r="P9" t="n">
-        <v>401.3512148301007</v>
+        <v>401.4166305533653</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -16536,7 +16582,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J330"/>
+  <dimension ref="A1:J331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -33699,6 +33745,58 @@
         </is>
       </c>
     </row>
+    <row r="331">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-05 22:11:45+00:00</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>-35.434344823410285,174.36202640265734</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>-35.4349875486223,174.36228579690894</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>-35.43558065180217,174.362703969962</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>-35.43614015519433,174.363212775724</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>-35.436635444219924,174.36379164864329</t>
+        </is>
+      </c>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>-35.437045631049564,174.36445285066014</t>
+        </is>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>-35.4373575608693,174.3651326481983</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>-35.437568014770044,174.3659294081705</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
